--- a/vehicle_log.xlsx
+++ b/vehicle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D410"/>
+  <dimension ref="A1:D411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9436,6 +9436,28 @@
         </is>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>MH12FU1014</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>11:52:24</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vehicle_log.xlsx
+++ b/vehicle_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D411"/>
+  <dimension ref="A1:D487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9458,6 +9458,1678 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>MH01DE2780</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>12:34:33</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>MH03AR5549</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>12:35:11</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>UP80DP1308</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>12:35:30</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>MH12FU1014</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>12:46:07</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>MH01DE2780</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>12:46:46</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>UP32AB1234</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>12:47:01</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>CRIMINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>MH20EE0943</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>12:48:36</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>01BG8283</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>12:52:45</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>AP318F1766</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>12:58:06</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>UP80DP1308</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>12:58:50</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>DP1308</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>12:59:21</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>12:59:21</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>24BH80218</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>12:59:25</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>24BH8021</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>12:59:26</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>12:59:26</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>4BH8021B</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>12:59:27</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>24BH80218</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>12:59:28</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>8021B</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>12:59:29</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>12:59:29</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>QQQCQ66OQGQ</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>12:59:39</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>12:59:40</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>24BH80218</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>12:59:42</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>12:59:43</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>CCGKCCOO</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>12:59:44</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>24BH80218</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>12:59:45</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>12:59:45</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>24BH80218</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>12:59:46</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>24BH8021B</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>12:59:47</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>MH12FU1014</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>17:05:52</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>UP80DP1308</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>17:07:01</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>UKO78G004</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>17:07:33</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>UKO7BG0040</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>17:07:35</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>220H9835A</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>17:07:37</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>22889835A</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>17:07:38</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>22BH9835A</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>17:07:38</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>228H9835A</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>17:07:39</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>22BH9835A</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>17:07:41</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>22BH9835AND</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>17:07:44</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>22BH9835A</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>17:07:45</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>DLD</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>17:07:49</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>22BH9835A</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>17:07:49</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>DID</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>17:07:50</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>228H11778</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>17:07:52</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>228H11770</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>17:07:53</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>228H11778</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>17:07:54</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>228811776</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>17:08:00</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>228H11778</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>17:08:00</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>MH12TD1795</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>17:08:02</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>MH12TD179</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>17:08:04</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>MH12TD17</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>17:08:04</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>MP18C0001TC</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>17:08:13</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>P18C0001T0</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>17:08:14</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>P18C0001TC</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>17:08:14</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>MP18C0001T</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>17:08:15</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>MP18C0001TO</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>17:08:16</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>MP18C0001T0</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>1P18C0001TC</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>17:08:18</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>MP18C0001TO</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>17:08:18</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>MP18C0001TC</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>17:08:19</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>24BH2345AA</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>17:08:24</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>BMH</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>17:08:29</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>KA12C6811</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>17:08:30</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>MH02VD26</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>17:08:31</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>02VD2636</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>17:08:31</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>MH02VD26</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>17:08:32</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>MH12FU1014</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>19:43:34</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>19R669</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>19:45:18</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>HR19RND</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>19:45:19</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>HR19R6</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>19:45:20</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>HR19RND</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>19:45:21</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>19R669</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>19:45:21</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>HR19R</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>19:45:22</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>19R669</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>19:45:23</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>HR19RND</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>19:45:24</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>19R669</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>19:45:24</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>UP80DP1308</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>19:45:37</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
